--- a/testdata/realdata/odf_terminals.xlsx
+++ b/testdata/realdata/odf_terminals.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C121"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +432,11 @@
           <t>对应纤芯</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -449,6 +454,11 @@
           <t>OC-HDQ|1</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -466,6 +476,11 @@
           <t>OC-HDQ|2</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -483,6 +498,11 @@
           <t>OC-HDQ|3</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -500,6 +520,11 @@
           <t>OC-HDQ|4</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -517,6 +542,11 @@
           <t>OC-HDQ|5</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -534,6 +564,11 @@
           <t>OC-HDQ|6</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -551,6 +586,11 @@
           <t>OC-HDQ|7</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -568,6 +608,11 @@
           <t>OC-HDQ|8</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -581,6 +626,11 @@
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -594,6 +644,11 @@
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -607,6 +662,11 @@
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -620,6 +680,11 @@
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -633,6 +698,11 @@
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -646,6 +716,11 @@
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -659,6 +734,11 @@
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -672,6 +752,11 @@
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -689,6 +774,11 @@
           <t>OC-QJ|1</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -706,6 +796,11 @@
           <t>OC-QJ|2</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -723,6 +818,11 @@
           <t>OC-QJ|3</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -740,6 +840,11 @@
           <t>OC-QJ|4</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -757,6 +862,11 @@
           <t>OC-QJ|5</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -774,6 +884,11 @@
           <t>OC-QJ|6</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -791,6 +906,11 @@
           <t>OC-QJ|7</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -808,6 +928,11 @@
           <t>OC-QJ|8</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -821,6 +946,11 @@
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -834,6 +964,11 @@
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -847,6 +982,11 @@
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -860,6 +1000,11 @@
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -873,6 +1018,11 @@
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -886,6 +1036,11 @@
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -899,6 +1054,11 @@
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -912,6 +1072,11 @@
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -925,6 +1090,11 @@
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -938,6 +1108,11 @@
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -951,6 +1126,11 @@
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -964,6 +1144,11 @@
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -977,6 +1162,11 @@
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -990,6 +1180,11 @@
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1003,6 +1198,11 @@
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1016,6 +1216,11 @@
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1033,6 +1238,11 @@
           <t>OC-JM2|1</t>
         </is>
       </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1050,6 +1260,11 @@
           <t>OC-JM2|2</t>
         </is>
       </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1067,6 +1282,11 @@
           <t>OC-JM2|3</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1084,6 +1304,11 @@
           <t>OC-JM2|4</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1101,6 +1326,11 @@
           <t>OC-JM2|5</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1118,6 +1348,11 @@
           <t>OC-JM2|6</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1135,6 +1370,11 @@
           <t>OC-JM2|7</t>
         </is>
       </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1152,6 +1392,11 @@
           <t>OC-JM2|8</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1165,6 +1410,11 @@
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1178,6 +1428,11 @@
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1191,6 +1446,11 @@
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1204,6 +1464,11 @@
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1217,6 +1482,11 @@
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1230,6 +1500,11 @@
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1243,6 +1518,11 @@
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1256,6 +1536,11 @@
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1269,6 +1554,11 @@
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1282,6 +1572,11 @@
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1295,6 +1590,11 @@
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1308,6 +1608,11 @@
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1321,6 +1626,11 @@
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1334,6 +1644,11 @@
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1347,6 +1662,11 @@
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1360,6 +1680,11 @@
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1373,6 +1698,11 @@
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1386,6 +1716,11 @@
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1399,6 +1734,11 @@
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1412,6 +1752,11 @@
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1425,6 +1770,11 @@
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1438,6 +1788,11 @@
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1451,6 +1806,11 @@
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1464,6 +1824,11 @@
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1481,6 +1846,11 @@
           <t>OC-JM|1</t>
         </is>
       </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1498,6 +1868,11 @@
           <t>OC-JM|2</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1515,6 +1890,11 @@
           <t>OC-JM|3</t>
         </is>
       </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1532,6 +1912,11 @@
           <t>OC-JM|4</t>
         </is>
       </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1549,6 +1934,11 @@
           <t>OC-JM|5</t>
         </is>
       </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1566,6 +1956,11 @@
           <t>OC-JM|6</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1583,6 +1978,11 @@
           <t>OC-JM|7</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1600,6 +2000,11 @@
           <t>OC-JM|8</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1613,6 +2018,11 @@
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1626,6 +2036,11 @@
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1639,6 +2054,11 @@
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1652,6 +2072,11 @@
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1665,6 +2090,11 @@
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1678,6 +2108,11 @@
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1691,6 +2126,11 @@
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1704,6 +2144,11 @@
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1717,6 +2162,11 @@
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1730,6 +2180,11 @@
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1743,6 +2198,11 @@
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1756,6 +2216,11 @@
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1769,6 +2234,11 @@
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1782,6 +2252,11 @@
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1795,6 +2270,11 @@
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1808,6 +2288,11 @@
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1821,6 +2306,11 @@
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1834,6 +2324,11 @@
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1847,6 +2342,11 @@
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1860,6 +2360,11 @@
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1873,6 +2378,11 @@
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1886,6 +2396,11 @@
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1899,6 +2414,11 @@
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1912,6 +2432,11 @@
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1925,6 +2450,11 @@
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1938,6 +2468,11 @@
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1951,6 +2486,11 @@
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1964,6 +2504,11 @@
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1977,6 +2522,11 @@
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1990,6 +2540,11 @@
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2003,6 +2558,11 @@
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2016,6 +2576,11 @@
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2029,6 +2594,11 @@
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2042,6 +2612,11 @@
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2055,6 +2630,11 @@
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2068,6 +2648,11 @@
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2081,6 +2666,11 @@
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2094,6 +2684,11 @@
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2107,6 +2702,11 @@
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2120,6 +2720,11 @@
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
